--- a/docs/StructureDefinition-dcs-risk-assessment.xlsx
+++ b/docs/StructureDefinition-dcs-risk-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-dcs-risk-assessment.xlsx
+++ b/docs/StructureDefinition-dcs-risk-assessment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="311">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/dcs-risk-assessment</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/dcs-risk-assessment</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -462,7 +465,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -622,7 +625,7 @@
     <t>RiskAssessment.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://mitre.org/fhir/space-health/StructureDefinition/Astronaut)
+    <t xml:space="preserve">Reference(https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/astronaut)
 </t>
   </si>
   <si>
@@ -1242,54 +1245,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1312,7 +1317,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="74.9921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.42578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1346,146 +1351,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1497,13 +1502,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1554,31 +1559,31 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>20</v>
@@ -1586,10 +1591,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1597,10 +1602,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1609,19 +1614,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1671,13 +1676,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1703,10 +1708,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1714,10 +1719,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1726,16 +1731,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1786,19 +1791,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1818,10 +1823,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1829,31 +1834,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1903,19 +1908,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1935,10 +1940,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1946,10 +1951,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1961,16 +1966,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1996,13 +2001,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2020,19 +2025,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2052,21 +2057,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2078,16 +2083,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2137,19 +2142,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2158,7 +2163,7 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>20</v>
@@ -2169,21 +2174,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2195,16 +2200,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2254,13 +2259,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2275,7 +2280,7 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>20</v>
@@ -2286,10 +2291,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2297,10 +2302,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2312,13 +2317,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2357,29 +2362,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2399,26 +2404,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -2427,13 +2432,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2484,19 +2489,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2516,45 +2521,45 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2603,19 +2608,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -2624,7 +2629,7 @@
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>20</v>
@@ -2635,10 +2640,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2646,10 +2651,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2658,16 +2663,16 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2718,42 +2723,42 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2761,10 +2766,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2776,13 +2781,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2833,22 +2838,22 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
@@ -2865,10 +2870,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2876,10 +2881,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2891,13 +2896,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2948,22 +2953,22 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
@@ -2980,10 +2985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2991,28 +2996,28 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3039,13 +3044,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3063,22 +3068,22 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
@@ -3090,15 +3095,15 @@
         <v>20</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3106,10 +3111,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3118,20 +3123,20 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3156,10 +3161,10 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z16" t="s" s="2">
         <v>20</v>
@@ -3180,19 +3185,19 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -3201,21 +3206,21 @@
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3223,10 +3228,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3235,16 +3240,16 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3295,22 +3300,22 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
@@ -3322,15 +3327,15 @@
         <v>20</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3338,28 +3343,28 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3410,42 +3415,42 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3453,10 +3458,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3465,16 +3470,16 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3525,42 +3530,42 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3568,32 +3573,32 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3642,42 +3647,42 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3685,10 +3690,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3697,16 +3702,16 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3757,19 +3762,19 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
@@ -3778,7 +3783,7 @@
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
@@ -3789,10 +3794,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3800,10 +3805,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -3812,16 +3817,16 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3872,42 +3877,42 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3915,10 +3920,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3930,13 +3935,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3987,22 +3992,22 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
@@ -4014,15 +4019,15 @@
         <v>20</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4030,10 +4035,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4045,13 +4050,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4102,42 +4107,42 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4145,13 +4150,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
@@ -4160,13 +4165,13 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4217,19 +4222,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -4238,10 +4243,10 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -4249,10 +4254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4260,13 +4265,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
@@ -4275,16 +4280,16 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4334,19 +4339,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -4355,7 +4360,7 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4366,10 +4371,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4377,10 +4382,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4392,13 +4397,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4449,13 +4454,13 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -4470,7 +4475,7 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
@@ -4481,21 +4486,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4507,16 +4512,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4566,19 +4571,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -4587,7 +4592,7 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
@@ -4598,45 +4603,45 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -4685,19 +4690,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -4706,7 +4711,7 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>20</v>
@@ -4717,10 +4722,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4728,13 +4733,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
@@ -4743,13 +4748,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4776,10 +4781,10 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>20</v>
@@ -4800,19 +4805,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -4821,10 +4826,10 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -4832,10 +4837,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4843,13 +4848,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
@@ -4858,16 +4863,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4917,19 +4922,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -4938,10 +4943,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -4949,10 +4954,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4960,10 +4965,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -4975,13 +4980,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5008,13 +5013,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5032,19 +5037,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5064,10 +5069,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5075,10 +5080,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5090,17 +5095,17 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5149,19 +5154,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5170,7 +5175,7 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -5181,10 +5186,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5192,10 +5197,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5207,16 +5212,16 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5266,19 +5271,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -5287,7 +5292,7 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -5298,10 +5303,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5309,10 +5314,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5324,13 +5329,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5381,19 +5386,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -5402,10 +5407,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -5413,10 +5418,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5424,10 +5429,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5439,17 +5444,17 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5498,19 +5503,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -5519,7 +5524,7 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -5530,10 +5535,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5541,10 +5546,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5556,13 +5561,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5613,22 +5618,22 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
